--- a/申請書/和裕申請書.xlsx
+++ b/申請書/和裕申請書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbf32e69ea87f61e/Desktop/申請書/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbf32e69ea87f61e/Desktop/claude/申請書/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="6" documentId="11_EB65238C7FD21B1DD866D8AEF0479755739B4146" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{088A7A4C-4400-4772-961B-2AB015FEEA9D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16110" yWindow="1245" windowWidth="19350" windowHeight="13485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="和裕維力貸" sheetId="7" r:id="rId1"/>
@@ -548,7 +548,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="236">
   <si>
     <t>期付款</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1289,10 +1289,6 @@
   </si>
   <si>
     <t>家用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同戶籍</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2115,6 +2111,37 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2123,17 +2150,92 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2144,6 +2246,17 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
@@ -2152,32 +2265,24 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2198,125 +2303,16 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3219,16 +3215,16 @@
       </c>
     </row>
     <row r="7" spans="2:43" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="82" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
       <c r="K7" s="6"/>
       <c r="R7" s="2" t="s">
         <v>68</v>
@@ -3319,15 +3315,15 @@
       <c r="B8" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="54"/>
-      <c r="D8" s="55"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="84"/>
       <c r="E8" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F8" s="54" t="s">
-        <v>213</v>
-      </c>
-      <c r="G8" s="55"/>
+      <c r="F8" s="83" t="s">
+        <v>212</v>
+      </c>
+      <c r="G8" s="84"/>
       <c r="I8" s="40"/>
       <c r="J8" s="8"/>
       <c r="Q8" s="2" t="s">
@@ -3347,10 +3343,10 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="56" t="s">
+      <c r="H9" s="75" t="s">
         <v>208</v>
       </c>
-      <c r="I9" s="56"/>
+      <c r="I9" s="75"/>
       <c r="Q9" s="2" t="s">
         <v>206</v>
       </c>
@@ -3362,16 +3358,16 @@
       </c>
     </row>
     <row r="10" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="59"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="47"/>
       <c r="J10" s="10"/>
       <c r="Q10" s="2" t="s">
         <v>207</v>
@@ -3441,19 +3437,19 @@
       <c r="B11" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="70" t="s">
-        <v>212</v>
-      </c>
-      <c r="D11" s="70"/>
+      <c r="C11" s="77" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="77"/>
       <c r="E11" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="F11" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="G11" s="70"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="61"/>
+      <c r="F11" s="77" t="s">
+        <v>218</v>
+      </c>
+      <c r="G11" s="77"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="94"/>
       <c r="J11" s="8"/>
       <c r="R11" s="2" t="s">
         <v>72</v>
@@ -3541,21 +3537,21 @@
       <c r="B12" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="D12" s="43"/>
+      <c r="C12" s="52" t="s">
+        <v>215</v>
+      </c>
+      <c r="D12" s="53"/>
       <c r="E12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F12" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="G12" s="43"/>
-      <c r="H12" s="68" t="s">
+      <c r="F12" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" s="53"/>
+      <c r="H12" s="89" t="s">
         <v>172</v>
       </c>
-      <c r="I12" s="69"/>
+      <c r="I12" s="90"/>
       <c r="R12" s="2" t="s">
         <v>73</v>
       </c>
@@ -3642,19 +3638,19 @@
       <c r="B13" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="43"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="F13" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="45"/>
+      <c r="F13" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="G13" s="53"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="92"/>
       <c r="Q13" s="2" t="s">
         <v>148</v>
       </c>
@@ -3744,21 +3740,21 @@
       <c r="B14" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="43"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F14" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="G14" s="43"/>
-      <c r="H14" s="93" t="s">
+      <c r="F14" s="52" t="s">
+        <v>220</v>
+      </c>
+      <c r="G14" s="53"/>
+      <c r="H14" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="I14" s="94"/>
+      <c r="I14" s="59"/>
       <c r="Q14" s="2" t="s">
         <v>149</v>
       </c>
@@ -3848,17 +3844,17 @@
       <c r="B15" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="48" t="s">
-        <v>220</v>
-      </c>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="67"/>
+      <c r="C15" s="80" t="s">
+        <v>219</v>
+      </c>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="88"/>
       <c r="G15" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="47"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="56"/>
       <c r="Q15" s="2" t="s">
         <v>150</v>
       </c>
@@ -3948,19 +3944,19 @@
       <c r="B16" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>211</v>
-      </c>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="67"/>
+      <c r="C16" s="80" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="88"/>
       <c r="G16" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="42" t="s">
+      <c r="H16" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="I16" s="47"/>
+      <c r="I16" s="56"/>
       <c r="Q16" s="2" t="s">
         <v>151</v>
       </c>
@@ -4050,10 +4046,10 @@
       <c r="B17" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C17" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="D17" s="43"/>
+      <c r="C17" s="52" t="s">
+        <v>220</v>
+      </c>
+      <c r="D17" s="53"/>
       <c r="E17" s="12" t="s">
         <v>195</v>
       </c>
@@ -4063,10 +4059,10 @@
       <c r="G17" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="H17" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="I17" s="47"/>
+      <c r="H17" s="52" t="s">
+        <v>221</v>
+      </c>
+      <c r="I17" s="56"/>
       <c r="Q17" s="2" t="s">
         <v>152</v>
       </c>
@@ -4081,22 +4077,22 @@
       <c r="B18" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="51"/>
-      <c r="E18" s="66"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="87"/>
       <c r="F18" s="14" t="s">
         <v>127</v>
       </c>
       <c r="G18" s="41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H18" s="14" t="s">
         <v>128</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>153</v>
@@ -4112,22 +4108,22 @@
       <c r="B19" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="88" t="s">
-        <v>229</v>
-      </c>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
+      <c r="C19" s="48" t="s">
+        <v>228</v>
+      </c>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
       <c r="F19" s="12" t="s">
         <v>130</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>131</v>
       </c>
       <c r="I19" s="29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>154</v>
@@ -4143,17 +4139,17 @@
       <c r="B20" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="72" t="s">
-        <v>230</v>
-      </c>
-      <c r="D20" s="73"/>
+      <c r="C20" s="54" t="s">
+        <v>229</v>
+      </c>
+      <c r="D20" s="55"/>
       <c r="E20" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="F20" s="62"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="64"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="96"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="97"/>
       <c r="Q20" s="2" t="s">
         <v>155</v>
       </c>
@@ -4191,17 +4187,17 @@
       </c>
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="B22" s="89" t="s">
+      <c r="B22" s="49" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="90"/>
+      <c r="C22" s="50"/>
       <c r="D22" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E22" s="91" t="s">
+      <c r="E22" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="F22" s="90"/>
+      <c r="F22" s="50"/>
       <c r="G22" s="4" t="s">
         <v>209</v>
       </c>
@@ -4246,17 +4242,17 @@
       <c r="B23" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="D23" s="43"/>
+      <c r="C23" s="52" t="s">
+        <v>224</v>
+      </c>
+      <c r="D23" s="53"/>
       <c r="E23" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="G23" s="47"/>
+      <c r="F23" s="52" t="s">
+        <v>223</v>
+      </c>
+      <c r="G23" s="56"/>
       <c r="Q23" s="2" t="s">
         <v>158</v>
       </c>
@@ -4322,17 +4318,17 @@
       <c r="B24" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C24" s="42" t="s">
-        <v>226</v>
-      </c>
-      <c r="D24" s="43"/>
+      <c r="C24" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="D24" s="53"/>
       <c r="E24" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="F24" s="42" t="s">
-        <v>228</v>
-      </c>
-      <c r="G24" s="47"/>
+      <c r="F24" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="G24" s="56"/>
       <c r="Q24" s="2" t="s">
         <v>159</v>
       </c>
@@ -4398,17 +4394,17 @@
       <c r="B25" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="72" t="s">
-        <v>223</v>
-      </c>
-      <c r="D25" s="73"/>
+      <c r="C25" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="D25" s="55"/>
       <c r="E25" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="72" t="s">
-        <v>227</v>
-      </c>
-      <c r="G25" s="92"/>
+      <c r="F25" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="G25" s="57"/>
       <c r="H25" s="2" t="s">
         <v>119</v>
       </c>
@@ -4586,19 +4582,19 @@
       </c>
     </row>
     <row r="27" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="98" t="s">
         <v>201</v>
       </c>
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="59"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="47"/>
       <c r="Q27" s="2" t="s">
         <v>162</v>
       </c>
@@ -4686,23 +4682,23 @@
       </c>
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A28" s="46"/>
+      <c r="A28" s="98"/>
       <c r="B28" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="D28" s="43"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="42" t="s">
+      <c r="F28" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="G28" s="43"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="91"/>
+      <c r="I28" s="92"/>
       <c r="Q28" s="2" t="s">
         <v>163</v>
       </c>
@@ -4790,21 +4786,21 @@
       </c>
     </row>
     <row r="29" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A29" s="46"/>
+      <c r="A29" s="98"/>
       <c r="B29" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="43"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="F29" s="42" t="s">
+      <c r="F29" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="G29" s="43"/>
+      <c r="G29" s="53"/>
       <c r="H29" s="12" t="s">
         <v>178</v>
       </c>
@@ -4893,23 +4889,23 @@
       </c>
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A30" s="46"/>
+      <c r="A30" s="98"/>
       <c r="B30" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="42"/>
-      <c r="D30" s="43"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="F30" s="42" t="s">
+      <c r="F30" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="G30" s="43"/>
-      <c r="H30" s="44" t="s">
+      <c r="G30" s="53"/>
+      <c r="H30" s="91" t="s">
         <v>181</v>
       </c>
-      <c r="I30" s="45"/>
+      <c r="I30" s="92"/>
       <c r="Q30" s="2" t="s">
         <v>165</v>
       </c>
@@ -4994,61 +4990,61 @@
       </c>
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A31" s="46"/>
+      <c r="A31" s="98"/>
       <c r="B31" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C31" s="48" t="s">
+      <c r="C31" s="80" t="s">
         <v>176</v>
       </c>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
       <c r="G31" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="H31" s="42"/>
-      <c r="I31" s="47"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="56"/>
       <c r="Q31" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A32" s="46"/>
+      <c r="A32" s="98"/>
       <c r="B32" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C32" s="48" t="s">
+      <c r="C32" s="80" t="s">
         <v>185</v>
       </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
       <c r="G32" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="42" t="s">
+      <c r="H32" s="52" t="s">
         <v>199</v>
       </c>
-      <c r="I32" s="47"/>
+      <c r="I32" s="56"/>
       <c r="Q32" s="2" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A33" s="46"/>
+      <c r="A33" s="98"/>
       <c r="B33" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="85" t="s">
         <v>176</v>
       </c>
-      <c r="D33" s="51"/>
+      <c r="D33" s="86"/>
       <c r="E33" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="F33" s="52"/>
-      <c r="G33" s="53"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="100"/>
       <c r="H33" s="14" t="s">
         <v>189</v>
       </c>
@@ -5112,13 +5108,13 @@
       </c>
     </row>
     <row r="34" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="46"/>
+      <c r="A34" s="98"/>
       <c r="B34" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="C34" s="84"/>
-      <c r="D34" s="84"/>
-      <c r="E34" s="84"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="79"/>
       <c r="F34" s="36" t="s">
         <v>191</v>
       </c>
@@ -5294,14 +5290,14 @@
       </c>
     </row>
     <row r="36" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="B36" s="74" t="s">
+      <c r="B36" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="C36" s="75"/>
-      <c r="D36" s="75"/>
-      <c r="E36" s="75"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="76"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="69"/>
       <c r="Q36" s="2" t="s">
         <v>145</v>
       </c>
@@ -5388,13 +5384,13 @@
       <c r="B37" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="C37" s="95" t="s">
-        <v>214</v>
-      </c>
-      <c r="D37" s="96"/>
-      <c r="E37" s="96"/>
-      <c r="F37" s="96"/>
-      <c r="G37" s="97"/>
+      <c r="C37" s="60" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="62"/>
       <c r="X37" s="2" t="s">
         <v>24</v>
       </c>
@@ -5478,13 +5474,13 @@
       <c r="B38" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C38" s="95" t="s">
-        <v>215</v>
-      </c>
-      <c r="D38" s="96"/>
-      <c r="E38" s="96"/>
-      <c r="F38" s="96"/>
-      <c r="G38" s="97"/>
+      <c r="C38" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="62"/>
       <c r="X38" s="2" t="s">
         <v>26</v>
       </c>
@@ -5568,14 +5564,14 @@
       <c r="B39" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="98" t="str">
+      <c r="C39" s="63" t="str">
         <f>C11</f>
         <v>詹馥慈</v>
       </c>
-      <c r="D39" s="99"/>
-      <c r="E39" s="99"/>
-      <c r="F39" s="99"/>
-      <c r="G39" s="100"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="65"/>
       <c r="Q39" s="2" t="s">
         <v>173</v>
       </c>
@@ -5659,87 +5655,87 @@
       </c>
     </row>
     <row r="40" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="71"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
       <c r="Q40" s="2" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="B41" s="85" t="s">
+      <c r="B41" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="86"/>
-      <c r="D41" s="86"/>
-      <c r="E41" s="86"/>
-      <c r="F41" s="86"/>
-      <c r="G41" s="87"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="44"/>
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B42" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="70" t="s">
-        <v>235</v>
-      </c>
-      <c r="D42" s="70"/>
+      <c r="C42" s="77" t="s">
+        <v>234</v>
+      </c>
+      <c r="D42" s="77"/>
       <c r="E42" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="F42" s="70" t="s">
-        <v>234</v>
-      </c>
-      <c r="G42" s="83"/>
+      <c r="F42" s="77" t="s">
+        <v>233</v>
+      </c>
+      <c r="G42" s="78"/>
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B43" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C43" s="70" t="s">
+      <c r="C43" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="70"/>
+      <c r="D43" s="77"/>
       <c r="E43" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="F43" s="70" t="s">
+      <c r="F43" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="G43" s="83"/>
+      <c r="G43" s="78"/>
     </row>
     <row r="44" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="78">
+      <c r="C44" s="71">
         <f xml:space="preserve"> VLOOKUP(F43,$Y$1:$AL$7,MATCH(C43,$Y$1:$AL$1,0),FALSE)</f>
         <v>6564</v>
       </c>
-      <c r="D44" s="78"/>
+      <c r="D44" s="71"/>
       <c r="E44" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F44" s="79">
+      <c r="F44" s="72">
         <f xml:space="preserve"> VLOOKUP(F43,$Y$10:$AL$16,MATCH(C43,$Y$10:$AL$10,0),FALSE)</f>
         <v>157536</v>
       </c>
-      <c r="G44" s="80"/>
+      <c r="G44" s="73"/>
     </row>
     <row r="45" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="77">
+      <c r="C45" s="70">
         <f>F44</f>
         <v>157536</v>
       </c>
-      <c r="D45" s="77"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="82"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="74"/>
+      <c r="F45" s="75"/>
+      <c r="G45" s="76"/>
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B47" s="5" t="s">
@@ -5799,6 +5795,56 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="z5QZqdGG19CI85gzb3YHj2+vVl4dWO/9L6Nh1clSYZeaRPt6GIUp547mUfphdfhIiKCo7gueR4ipCcsVudIjsQ==" saltValue="ANJ12Z4WoisMKg6+D2V2Ng==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="66">
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C19:E19"/>
@@ -5815,56 +5861,6 @@
     <mergeCell ref="C37:G37"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="10">

--- a/申請書/和裕申請書.xlsx
+++ b/申請書/和裕申請書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbf32e69ea87f61e/Desktop/claude/申請書/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_EB65238C7FD21B1DD866D8AEF0479755739B4146" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{088A7A4C-4400-4772-961B-2AB015FEEA9D}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_EB65238C7FD21B1DD866D8AEF0479755739B4146" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36882C59-3092-4866-AD11-B840E6BABB3B}"/>
   <bookViews>
-    <workbookView xWindow="16110" yWindow="1245" windowWidth="19350" windowHeight="13485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1275" yWindow="930" windowWidth="19350" windowHeight="13485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="和裕維力貸" sheetId="7" r:id="rId1"/>
@@ -2111,6 +2111,156 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2118,15 +2268,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2142,26 +2283,6 @@
     <xf numFmtId="49" fontId="2" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2192,127 +2313,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3215,16 +3215,16 @@
       </c>
     </row>
     <row r="7" spans="2:43" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="82" t="s">
+      <c r="B7" s="65" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="65"/>
       <c r="K7" s="6"/>
       <c r="R7" s="2" t="s">
         <v>68</v>
@@ -3315,15 +3315,15 @@
       <c r="B8" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="84"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="55"/>
       <c r="E8" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F8" s="83" t="s">
+      <c r="F8" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="G8" s="84"/>
+      <c r="G8" s="55"/>
       <c r="I8" s="40"/>
       <c r="J8" s="8"/>
       <c r="Q8" s="2" t="s">
@@ -3343,10 +3343,10 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="75" t="s">
+      <c r="H9" s="56" t="s">
         <v>208</v>
       </c>
-      <c r="I9" s="75"/>
+      <c r="I9" s="56"/>
       <c r="Q9" s="2" t="s">
         <v>206</v>
       </c>
@@ -3358,16 +3358,16 @@
       </c>
     </row>
     <row r="10" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="47"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="59"/>
       <c r="J10" s="10"/>
       <c r="Q10" s="2" t="s">
         <v>207</v>
@@ -3437,19 +3437,19 @@
       <c r="B11" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="77" t="s">
+      <c r="C11" s="70" t="s">
         <v>211</v>
       </c>
-      <c r="D11" s="77"/>
+      <c r="D11" s="70"/>
       <c r="E11" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="70" t="s">
         <v>218</v>
       </c>
-      <c r="G11" s="77"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="94"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="61"/>
       <c r="J11" s="8"/>
       <c r="R11" s="2" t="s">
         <v>72</v>
@@ -3537,21 +3537,21 @@
       <c r="B12" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="D12" s="53"/>
+      <c r="D12" s="43"/>
       <c r="E12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="42" t="s">
         <v>216</v>
       </c>
-      <c r="G12" s="53"/>
-      <c r="H12" s="89" t="s">
+      <c r="G12" s="43"/>
+      <c r="H12" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="I12" s="90"/>
+      <c r="I12" s="69"/>
       <c r="R12" s="2" t="s">
         <v>73</v>
       </c>
@@ -3638,19 +3638,19 @@
       <c r="B13" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="53"/>
+      <c r="D13" s="43"/>
       <c r="E13" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="F13" s="52" t="s">
+      <c r="F13" s="42" t="s">
         <v>217</v>
       </c>
-      <c r="G13" s="53"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="92"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="45"/>
       <c r="Q13" s="2" t="s">
         <v>148</v>
       </c>
@@ -3740,21 +3740,21 @@
       <c r="B14" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="52" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="53"/>
+      <c r="C14" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="43"/>
       <c r="E14" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F14" s="52" t="s">
+      <c r="F14" s="42" t="s">
         <v>220</v>
       </c>
-      <c r="G14" s="53"/>
-      <c r="H14" s="58" t="s">
+      <c r="G14" s="43"/>
+      <c r="H14" s="93" t="s">
         <v>119</v>
       </c>
-      <c r="I14" s="59"/>
+      <c r="I14" s="94"/>
       <c r="Q14" s="2" t="s">
         <v>149</v>
       </c>
@@ -3844,17 +3844,17 @@
       <c r="B15" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="80" t="s">
+      <c r="C15" s="48" t="s">
         <v>219</v>
       </c>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="88"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="67"/>
       <c r="G15" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H15" s="52"/>
-      <c r="I15" s="56"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="47"/>
       <c r="Q15" s="2" t="s">
         <v>150</v>
       </c>
@@ -3944,19 +3944,19 @@
       <c r="B16" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C16" s="80" t="s">
+      <c r="C16" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="88"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="67"/>
       <c r="G16" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="I16" s="56"/>
+      <c r="I16" s="47"/>
       <c r="Q16" s="2" t="s">
         <v>151</v>
       </c>
@@ -4046,10 +4046,10 @@
       <c r="B17" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C17" s="52" t="s">
+      <c r="C17" s="42" t="s">
         <v>220</v>
       </c>
-      <c r="D17" s="53"/>
+      <c r="D17" s="43"/>
       <c r="E17" s="12" t="s">
         <v>195</v>
       </c>
@@ -4059,10 +4059,10 @@
       <c r="G17" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="I17" s="56"/>
+      <c r="I17" s="47"/>
       <c r="Q17" s="2" t="s">
         <v>152</v>
       </c>
@@ -4077,11 +4077,11 @@
       <c r="B18" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="85" t="s">
+      <c r="C18" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="86"/>
-      <c r="E18" s="87"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="66"/>
       <c r="F18" s="14" t="s">
         <v>127</v>
       </c>
@@ -4108,11 +4108,11 @@
       <c r="B19" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="88" t="s">
         <v>228</v>
       </c>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
       <c r="F19" s="12" t="s">
         <v>130</v>
       </c>
@@ -4139,17 +4139,17 @@
       <c r="B20" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="72" t="s">
         <v>229</v>
       </c>
-      <c r="D20" s="55"/>
+      <c r="D20" s="73"/>
       <c r="E20" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="F20" s="95"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="97"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="64"/>
       <c r="Q20" s="2" t="s">
         <v>155</v>
       </c>
@@ -4187,17 +4187,17 @@
       </c>
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="B22" s="49" t="s">
+      <c r="B22" s="89" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="50"/>
+      <c r="C22" s="90"/>
       <c r="D22" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E22" s="51" t="s">
+      <c r="E22" s="91" t="s">
         <v>133</v>
       </c>
-      <c r="F22" s="50"/>
+      <c r="F22" s="90"/>
       <c r="G22" s="4" t="s">
         <v>209</v>
       </c>
@@ -4242,17 +4242,17 @@
       <c r="B23" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="D23" s="53"/>
+      <c r="D23" s="43"/>
       <c r="E23" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="52" t="s">
+      <c r="F23" s="42" t="s">
         <v>223</v>
       </c>
-      <c r="G23" s="56"/>
+      <c r="G23" s="47"/>
       <c r="Q23" s="2" t="s">
         <v>158</v>
       </c>
@@ -4318,17 +4318,17 @@
       <c r="B24" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C24" s="52" t="s">
+      <c r="C24" s="42" t="s">
         <v>225</v>
       </c>
-      <c r="D24" s="53"/>
+      <c r="D24" s="43"/>
       <c r="E24" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="F24" s="52" t="s">
+      <c r="F24" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="G24" s="56"/>
+      <c r="G24" s="47"/>
       <c r="Q24" s="2" t="s">
         <v>159</v>
       </c>
@@ -4394,17 +4394,17 @@
       <c r="B25" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="54" t="s">
+      <c r="C25" s="72" t="s">
         <v>222</v>
       </c>
-      <c r="D25" s="55"/>
+      <c r="D25" s="73"/>
       <c r="E25" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="54" t="s">
+      <c r="F25" s="72" t="s">
         <v>226</v>
       </c>
-      <c r="G25" s="57"/>
+      <c r="G25" s="92"/>
       <c r="H25" s="2" t="s">
         <v>119</v>
       </c>
@@ -4582,19 +4582,19 @@
       </c>
     </row>
     <row r="27" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A27" s="98" t="s">
+      <c r="A27" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="57" t="s">
         <v>200</v>
       </c>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="47"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="59"/>
       <c r="Q27" s="2" t="s">
         <v>162</v>
       </c>
@@ -4682,23 +4682,23 @@
       </c>
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A28" s="98"/>
+      <c r="A28" s="46"/>
       <c r="B28" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="D28" s="53"/>
+      <c r="D28" s="43"/>
       <c r="E28" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="52" t="s">
+      <c r="F28" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="G28" s="53"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="92"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="45"/>
       <c r="Q28" s="2" t="s">
         <v>163</v>
       </c>
@@ -4786,21 +4786,21 @@
       </c>
     </row>
     <row r="29" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A29" s="98"/>
+      <c r="A29" s="46"/>
       <c r="B29" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="53"/>
+      <c r="D29" s="43"/>
       <c r="E29" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="F29" s="52" t="s">
+      <c r="F29" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="G29" s="53"/>
+      <c r="G29" s="43"/>
       <c r="H29" s="12" t="s">
         <v>178</v>
       </c>
@@ -4889,23 +4889,23 @@
       </c>
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A30" s="98"/>
+      <c r="A30" s="46"/>
       <c r="B30" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="53"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="43"/>
       <c r="E30" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="F30" s="52" t="s">
+      <c r="F30" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="G30" s="53"/>
-      <c r="H30" s="91" t="s">
+      <c r="G30" s="43"/>
+      <c r="H30" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="I30" s="92"/>
+      <c r="I30" s="45"/>
       <c r="Q30" s="2" t="s">
         <v>165</v>
       </c>
@@ -4990,61 +4990,61 @@
       </c>
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A31" s="98"/>
+      <c r="A31" s="46"/>
       <c r="B31" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C31" s="80" t="s">
+      <c r="C31" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
       <c r="G31" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="H31" s="52"/>
-      <c r="I31" s="56"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="47"/>
       <c r="Q31" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A32" s="98"/>
+      <c r="A32" s="46"/>
       <c r="B32" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C32" s="80" t="s">
+      <c r="C32" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="49"/>
       <c r="G32" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="52" t="s">
+      <c r="H32" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="I32" s="56"/>
+      <c r="I32" s="47"/>
       <c r="Q32" s="2" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A33" s="98"/>
+      <c r="A33" s="46"/>
       <c r="B33" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C33" s="85" t="s">
+      <c r="C33" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="D33" s="86"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="F33" s="99"/>
-      <c r="G33" s="100"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="53"/>
       <c r="H33" s="14" t="s">
         <v>189</v>
       </c>
@@ -5108,13 +5108,13 @@
       </c>
     </row>
     <row r="34" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="98"/>
+      <c r="A34" s="46"/>
       <c r="B34" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
+      <c r="C34" s="84"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="84"/>
       <c r="F34" s="36" t="s">
         <v>191</v>
       </c>
@@ -5290,14 +5290,14 @@
       </c>
     </row>
     <row r="36" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="B36" s="67" t="s">
+      <c r="B36" s="74" t="s">
         <v>139</v>
       </c>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="69"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="76"/>
       <c r="Q36" s="2" t="s">
         <v>145</v>
       </c>
@@ -5384,13 +5384,13 @@
       <c r="B37" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="C37" s="60" t="s">
+      <c r="C37" s="95" t="s">
         <v>213</v>
       </c>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="62"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="96"/>
+      <c r="F37" s="96"/>
+      <c r="G37" s="97"/>
       <c r="X37" s="2" t="s">
         <v>24</v>
       </c>
@@ -5474,13 +5474,13 @@
       <c r="B38" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C38" s="60" t="s">
+      <c r="C38" s="95" t="s">
         <v>214</v>
       </c>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="62"/>
+      <c r="D38" s="96"/>
+      <c r="E38" s="96"/>
+      <c r="F38" s="96"/>
+      <c r="G38" s="97"/>
       <c r="X38" s="2" t="s">
         <v>26</v>
       </c>
@@ -5564,14 +5564,14 @@
       <c r="B39" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="63" t="str">
+      <c r="C39" s="98" t="str">
         <f>C11</f>
         <v>詹馥慈</v>
       </c>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="65"/>
+      <c r="D39" s="99"/>
+      <c r="E39" s="99"/>
+      <c r="F39" s="99"/>
+      <c r="G39" s="100"/>
       <c r="Q39" s="2" t="s">
         <v>173</v>
       </c>
@@ -5655,87 +5655,87 @@
       </c>
     </row>
     <row r="40" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
       <c r="Q40" s="2" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="B41" s="42" t="s">
+      <c r="B41" s="85" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="44"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="86"/>
+      <c r="E41" s="86"/>
+      <c r="F41" s="86"/>
+      <c r="G41" s="87"/>
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B42" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="77" t="s">
+      <c r="C42" s="70" t="s">
         <v>234</v>
       </c>
-      <c r="D42" s="77"/>
+      <c r="D42" s="70"/>
       <c r="E42" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="F42" s="77" t="s">
+      <c r="F42" s="70" t="s">
         <v>233</v>
       </c>
-      <c r="G42" s="78"/>
+      <c r="G42" s="83"/>
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B43" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="77"/>
+      <c r="D43" s="70"/>
       <c r="E43" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="F43" s="77" t="s">
+      <c r="F43" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="G43" s="78"/>
+      <c r="G43" s="83"/>
     </row>
     <row r="44" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="71">
+      <c r="C44" s="78">
         <f xml:space="preserve"> VLOOKUP(F43,$Y$1:$AL$7,MATCH(C43,$Y$1:$AL$1,0),FALSE)</f>
         <v>6564</v>
       </c>
-      <c r="D44" s="71"/>
+      <c r="D44" s="78"/>
       <c r="E44" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F44" s="72">
+      <c r="F44" s="79">
         <f xml:space="preserve"> VLOOKUP(F43,$Y$10:$AL$16,MATCH(C43,$Y$10:$AL$10,0),FALSE)</f>
         <v>157536</v>
       </c>
-      <c r="G44" s="73"/>
+      <c r="G44" s="80"/>
     </row>
     <row r="45" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="70">
+      <c r="C45" s="77">
         <f>F44</f>
         <v>157536</v>
       </c>
-      <c r="D45" s="70"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="75"/>
-      <c r="G45" s="76"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="82"/>
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B47" s="5" t="s">
@@ -5795,24 +5795,38 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="z5QZqdGG19CI85gzb3YHj2+vVl4dWO/9L6Nh1clSYZeaRPt6GIUp547mUfphdfhIiKCo7gueR4ipCcsVudIjsQ==" saltValue="ANJ12Z4WoisMKg6+D2V2Ng==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="66">
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C17:D17"/>
@@ -5829,38 +5843,24 @@
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="10">
